--- a/output/pdf_financials_xlsx/LSL.xlsx
+++ b/output/pdf_financials_xlsx/LSL.xlsx
@@ -3234,7 +3234,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LSL.xlsx
+++ b/output/pdf_financials_xlsx/LSL.xlsx
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>2.971</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-4.74</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0</v>
@@ -2670,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.361</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="117">
@@ -6384,7 +6384,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>2.561</v>
       </c>
@@ -7030,7 +7034,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -7900,7 +7908,11 @@
           <t>Deferred income tax expenses 19</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -8150,7 +8162,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -8550,7 +8566,11 @@
           <t>Net change in non-cash operating working capital items 21</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>2.971</v>
       </c>
@@ -8618,7 +8638,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
